--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -678,7 +693,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -759,7 +774,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -840,7 +855,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -921,7 +936,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1002,7 +1017,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1083,7 +1098,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1164,7 +1179,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1245,7 +1260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1326,7 +1341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1407,7 +1422,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1488,7 +1503,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1569,7 +1584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1650,7 +1665,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1731,7 +1746,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1812,7 +1827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1893,7 +1908,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1974,7 +1989,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2055,7 +2070,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2136,7 +2151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2217,7 +2232,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2298,7 +2313,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2379,7 +2394,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2460,7 +2475,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2541,7 +2556,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2622,7 +2637,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2703,7 +2718,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2784,7 +2799,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2865,7 +2880,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2946,7 +2961,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3027,7 +3042,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3108,7 +3123,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3189,7 +3204,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3270,7 +3285,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3351,7 +3366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3432,7 +3447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3513,7 +3528,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3594,7 +3609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3675,7 +3690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3756,7 +3771,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3837,7 +3852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3918,7 +3933,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3999,7 +4014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4080,7 +4095,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4161,7 +4176,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4242,7 +4257,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4323,7 +4338,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4404,7 +4419,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4485,7 +4500,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4566,7 +4581,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4647,7 +4662,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4728,7 +4743,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4809,7 +4824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4890,7 +4905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4971,7 +4986,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5052,7 +5067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -5133,7 +5148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5214,7 +5229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5295,7 +5310,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5376,7 +5391,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5457,7 +5472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5538,7 +5553,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5619,7 +5634,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5700,7 +5715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5781,7 +5796,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5862,7 +5877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5943,7 +5958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6024,7 +6039,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -6105,7 +6120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6186,7 +6201,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6267,7 +6282,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6348,7 +6363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6429,7 +6444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6510,7 +6525,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6591,7 +6606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6672,7 +6687,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6753,7 +6768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6834,7 +6849,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6915,7 +6930,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6996,7 +7011,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -7077,7 +7092,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -7158,7 +7173,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7239,7 +7254,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7320,7 +7335,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7401,7 +7416,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7482,7 +7497,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7563,7 +7578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7644,7 +7659,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7725,7 +7740,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7806,7 +7821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7887,7 +7902,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7968,7 +7983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -8049,7 +8064,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -8130,7 +8145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8211,7 +8226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8292,7 +8307,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8373,7 +8388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8454,7 +8469,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8535,7 +8550,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8616,7 +8631,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8697,7 +8712,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8778,7 +8793,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8859,7 +8874,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8940,7 +8955,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -9021,7 +9036,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -9102,7 +9117,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -9183,7 +9198,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9264,7 +9279,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9345,7 +9360,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9426,7 +9441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9507,7 +9522,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9588,7 +9603,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9669,7 +9684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9750,7 +9765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9831,7 +9846,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9912,7 +9927,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9993,7 +10008,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -10074,7 +10089,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -10155,7 +10170,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10236,7 +10251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10317,7 +10332,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10398,7 +10413,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10479,7 +10494,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10560,7 +10575,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10641,7 +10656,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10722,7 +10737,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10803,7 +10818,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10884,7 +10899,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10965,7 +10980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -11046,7 +11061,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -11127,7 +11142,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11208,7 +11223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11289,7 +11304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11370,7 +11385,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11451,7 +11466,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11532,7 +11547,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11613,7 +11628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11694,7 +11709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11775,7 +11790,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11856,7 +11871,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11937,7 +11952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -12018,7 +12033,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -12099,7 +12114,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -12180,7 +12195,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12261,7 +12276,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12342,7 +12357,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12423,7 +12438,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12504,7 +12519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12585,7 +12600,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12666,7 +12681,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12747,7 +12762,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12828,7 +12843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12909,7 +12924,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12990,7 +13005,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -13071,7 +13086,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -13152,7 +13167,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -13233,7 +13248,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13314,7 +13329,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13395,7 +13410,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13476,7 +13491,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13557,7 +13572,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13638,7 +13653,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13719,7 +13734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13800,7 +13815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13881,7 +13896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13962,7 +13977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -14043,7 +14058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -14124,7 +14139,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -14205,7 +14220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -14286,7 +14301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14367,7 +14382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14448,7 +14463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14529,7 +14544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14610,7 +14625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14691,7 +14706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14772,7 +14787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14853,7 +14868,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14934,7 +14949,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -15015,7 +15030,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -15096,7 +15111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -15177,7 +15192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -15258,7 +15273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -15339,7 +15354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15420,7 +15435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15501,7 +15516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15582,7 +15597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15663,7 +15678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15744,7 +15759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15825,7 +15840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15906,7 +15921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15987,7 +16002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -16068,7 +16083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -16149,7 +16164,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -16230,7 +16245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -16311,7 +16326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -16392,7 +16407,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16473,7 +16488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16554,7 +16569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16635,7 +16650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16716,7 +16731,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16797,7 +16812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16878,7 +16893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16959,7 +16974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -17040,7 +17055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -17121,7 +17136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -17202,7 +17217,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -17283,7 +17298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -17364,7 +17379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17445,7 +17460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17526,7 +17541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17607,7 +17622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17688,7 +17703,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17769,7 +17784,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17850,7 +17865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17931,7 +17946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -18012,7 +18027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -18093,7 +18108,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -18174,7 +18189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -18255,7 +18270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -18336,7 +18351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -18417,7 +18432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18498,7 +18513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18579,7 +18594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18660,7 +18675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18741,7 +18756,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18822,7 +18837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18903,7 +18918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18984,7 +18999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -19065,7 +19080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -19146,7 +19161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -19227,7 +19242,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -19308,7 +19323,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -19389,7 +19404,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -19470,7 +19485,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19551,7 +19566,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19632,7 +19647,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19713,7 +19728,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19794,7 +19809,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19875,7 +19890,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19956,7 +19971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -20037,7 +20052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -20118,7 +20133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -20199,7 +20214,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -20280,7 +20295,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -20361,7 +20376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -20442,7 +20457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -20523,7 +20538,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20604,7 +20619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20685,7 +20700,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20766,7 +20781,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20847,7 +20862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20928,7 +20943,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -21009,7 +21024,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -21090,7 +21105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -21171,7 +21186,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -21252,7 +21267,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -21333,7 +21348,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -21414,7 +21429,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -21495,7 +21510,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21576,7 +21591,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21657,7 +21672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21738,7 +21753,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21819,7 +21834,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21900,7 +21915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21981,7 +21996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -22062,7 +22077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -22143,7 +22158,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -22224,7 +22239,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -22305,7 +22320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -22386,7 +22401,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -22467,7 +22482,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -22548,7 +22563,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -22629,7 +22644,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -22710,7 +22725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -22791,7 +22806,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22872,7 +22887,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22953,7 +22968,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -23034,7 +23049,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -23115,7 +23130,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -23196,7 +23211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -23277,7 +23292,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -23358,7 +23373,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -23439,7 +23454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -23520,7 +23535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -23601,7 +23616,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -23682,7 +23697,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -23763,7 +23778,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -23844,7 +23859,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23925,7 +23940,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -24006,7 +24021,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -24087,7 +24102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -24168,7 +24183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -24249,7 +24264,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -24330,7 +24345,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -24411,7 +24426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -24492,7 +24507,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -24573,7 +24588,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -24654,7 +24669,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -24735,7 +24750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -24816,7 +24831,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -24897,7 +24912,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24978,7 +24993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -25059,7 +25074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -25140,7 +25155,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -25221,7 +25236,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -25302,7 +25317,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -25383,7 +25398,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -25464,7 +25479,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -25545,7 +25560,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -25626,7 +25641,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -25707,7 +25722,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -25788,7 +25803,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -25869,7 +25884,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -25950,7 +25965,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -26031,7 +26046,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -26112,7 +26127,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -26193,7 +26208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -26274,7 +26289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -26355,7 +26370,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -26436,7 +26451,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -26517,7 +26532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -26598,7 +26613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -26679,7 +26694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -26760,7 +26775,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -26841,7 +26856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -26922,7 +26937,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -27003,7 +27018,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -27084,7 +27099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -27165,7 +27180,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -27246,7 +27261,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -27327,7 +27342,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -27408,7 +27423,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -27489,7 +27504,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -27570,7 +27585,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -27651,7 +27666,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G341" s="4" t="n">
+      <c r="G341" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -27732,7 +27747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G342" s="4" t="n">
+      <c r="G342" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -27813,7 +27828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G343" s="4" t="n">
+      <c r="G343" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -27894,7 +27909,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G344" s="4" t="n">
+      <c r="G344" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -27975,7 +27990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n">
+      <c r="G345" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -28056,7 +28071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n">
+      <c r="G346" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -28137,7 +28152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n">
+      <c r="G347" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -28218,7 +28233,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n">
+      <c r="G348" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -28299,7 +28314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G349" s="4" t="n">
+      <c r="G349" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -28380,7 +28395,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G350" s="4" t="n">
+      <c r="G350" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -28461,7 +28476,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G351" s="4" t="n">
+      <c r="G351" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -28542,7 +28557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G352" s="4" t="n">
+      <c r="G352" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
@@ -28623,7 +28638,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G353" s="4" t="n">
+      <c r="G353" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
@@ -28704,7 +28719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G354" s="4" t="n">
+      <c r="G354" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
@@ -28785,7 +28800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G355" s="4" t="n">
+      <c r="G355" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
@@ -28866,7 +28881,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G356" s="4" t="n">
+      <c r="G356" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -28947,7 +28962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G357" s="4" t="n">
+      <c r="G357" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -29028,7 +29043,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G358" s="4" t="n">
+      <c r="G358" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -29109,7 +29124,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G359" s="4" t="n">
+      <c r="G359" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -29190,7 +29205,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n">
+      <c r="G360" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
@@ -29271,7 +29286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G361" s="4" t="n">
+      <c r="G361" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
@@ -29352,7 +29367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G362" s="4" t="n">
+      <c r="G362" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
@@ -29433,7 +29448,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G363" s="4" t="n">
+      <c r="G363" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
@@ -29514,7 +29529,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G364" s="4" t="n">
+      <c r="G364" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -29595,7 +29610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G365" s="4" t="n">
+      <c r="G365" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
@@ -29676,7 +29691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G366" s="4" t="n">
+      <c r="G366" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
@@ -29757,7 +29772,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G367" s="4" t="n">
+      <c r="G367" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
@@ -29838,7 +29853,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G368" s="4" t="n">
+      <c r="G368" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
@@ -29919,7 +29934,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G369" s="4" t="n">
+      <c r="G369" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -30000,7 +30015,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G370" s="4" t="n">
+      <c r="G370" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -30081,7 +30096,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G371" s="4" t="n">
+      <c r="G371" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -30162,7 +30177,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G372" s="4" t="n">
+      <c r="G372" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -30243,7 +30258,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G373" s="4" t="n">
+      <c r="G373" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -30324,7 +30339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G374" s="4" t="n">
+      <c r="G374" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -30405,7 +30420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G375" s="4" t="n">
+      <c r="G375" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -30486,7 +30501,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G376" s="4" t="n">
+      <c r="G376" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -30567,7 +30582,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G377" s="4" t="n">
+      <c r="G377" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -30648,7 +30663,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G378" s="4" t="n">
+      <c r="G378" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
@@ -30729,7 +30744,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G379" s="4" t="n">
+      <c r="G379" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
@@ -30810,7 +30825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G380" s="4" t="n">
+      <c r="G380" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -30891,7 +30906,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G381" s="4" t="n">
+      <c r="G381" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -30972,7 +30987,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G382" s="4" t="n">
+      <c r="G382" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -31053,7 +31068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G383" s="4" t="n">
+      <c r="G383" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -31134,7 +31149,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G384" s="4" t="n">
+      <c r="G384" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -31215,7 +31230,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G385" s="4" t="n">
+      <c r="G385" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -31296,7 +31311,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G386" s="4" t="n">
+      <c r="G386" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -31377,7 +31392,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
+      <c r="G387" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -31458,7 +31473,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G388" s="4" t="n">
+      <c r="G388" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
@@ -31539,7 +31554,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G389" s="4" t="n">
+      <c r="G389" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -31620,7 +31635,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G390" s="4" t="n">
+      <c r="G390" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
@@ -31701,7 +31716,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G391" s="4" t="n">
+      <c r="G391" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -31782,7 +31797,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G392" s="4" t="n">
+      <c r="G392" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -31863,7 +31878,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G393" s="4" t="n">
+      <c r="G393" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -31944,7 +31959,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G394" s="4" t="n">
+      <c r="G394" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -32025,7 +32040,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G395" s="4" t="n">
+      <c r="G395" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -32106,7 +32121,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G396" s="4" t="n">
+      <c r="G396" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -32187,7 +32202,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G397" s="4" t="n">
+      <c r="G397" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -32268,7 +32283,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n">
+      <c r="G398" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -32349,7 +32364,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G399" s="4" t="n">
+      <c r="G399" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -32430,7 +32445,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G400" s="4" t="n">
+      <c r="G400" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -32511,7 +32526,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G401" s="4" t="n">
+      <c r="G401" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -32592,7 +32607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G402" s="4" t="n">
+      <c r="G402" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -32673,7 +32688,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G403" s="4" t="n">
+      <c r="G403" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -32754,7 +32769,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G404" s="4" t="n">
+      <c r="G404" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -32835,7 +32850,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n">
+      <c r="G405" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -32916,7 +32931,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G406" s="4" t="n">
+      <c r="G406" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -32997,7 +33012,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G407" s="4" t="n">
+      <c r="G407" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -33078,7 +33093,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G408" s="4" t="n">
+      <c r="G408" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -33159,7 +33174,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G409" s="4" t="n">
+      <c r="G409" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -33240,7 +33255,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G410" s="4" t="n">
+      <c r="G410" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -33321,7 +33336,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G411" s="4" t="n">
+      <c r="G411" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -33402,7 +33417,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G412" s="4" t="n">
+      <c r="G412" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -33483,7 +33498,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G413" s="4" t="n">
+      <c r="G413" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -33564,7 +33579,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G414" s="4" t="n">
+      <c r="G414" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -33645,7 +33660,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G415" s="4" t="n">
+      <c r="G415" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -33726,7 +33741,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G416" s="4" t="n">
+      <c r="G416" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -33807,7 +33822,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G417" s="4" t="n">
+      <c r="G417" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -33888,7 +33903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G418" s="4" t="n">
+      <c r="G418" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -33969,7 +33984,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G419" s="4" t="n">
+      <c r="G419" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -34050,7 +34065,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G420" s="4" t="n">
+      <c r="G420" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -34131,7 +34146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G421" s="4" t="n">
+      <c r="G421" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -34212,7 +34227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G422" s="4" t="n">
+      <c r="G422" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -34293,7 +34308,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n">
+      <c r="G423" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -34374,7 +34389,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n">
+      <c r="G424" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -34455,7 +34470,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n">
+      <c r="G425" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -34536,7 +34551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n">
+      <c r="G426" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -34617,7 +34632,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G427" s="4" t="n">
+      <c r="G427" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -34698,7 +34713,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G428" s="4" t="n">
+      <c r="G428" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -34779,7 +34794,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G429" s="4" t="n">
+      <c r="G429" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -34860,7 +34875,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G430" s="4" t="n">
+      <c r="G430" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
@@ -34941,7 +34956,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G431" s="4" t="n">
+      <c r="G431" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
@@ -35022,7 +35037,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G432" s="4" t="n">
+      <c r="G432" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -35103,7 +35118,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G433" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
@@ -35184,7 +35199,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G434" s="4" t="n">
+      <c r="G434" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
@@ -35265,7 +35280,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G435" s="4" t="n">
+      <c r="G435" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
@@ -35346,7 +35361,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G436" s="4" t="n">
+      <c r="G436" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
@@ -35427,7 +35442,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G437" s="4" t="n">
+      <c r="G437" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
@@ -35508,7 +35523,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G438" s="4" t="n">
+      <c r="G438" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
@@ -35589,7 +35604,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G439" s="4" t="n">
+      <c r="G439" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
@@ -35670,7 +35685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G440" s="4" t="n">
+      <c r="G440" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
@@ -35751,7 +35766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G441" s="4" t="n">
+      <c r="G441" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
@@ -35832,7 +35847,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G442" s="4" t="n">
+      <c r="G442" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
@@ -35913,7 +35928,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G443" s="4" t="n">
+      <c r="G443" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
@@ -35994,7 +36009,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G444" s="4" t="n">
+      <c r="G444" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
@@ -36075,7 +36090,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G445" s="4" t="n">
+      <c r="G445" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
@@ -36156,7 +36171,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G446" s="4" t="n">
+      <c r="G446" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
@@ -36237,7 +36252,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G447" s="4" t="n">
+      <c r="G447" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
@@ -36318,7 +36333,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G448" s="4" t="n">
+      <c r="G448" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
@@ -36399,7 +36414,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G449" s="4" t="n">
+      <c r="G449" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
@@ -36480,7 +36495,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n">
+      <c r="G450" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
@@ -36561,7 +36576,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n">
+      <c r="G451" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
@@ -36642,7 +36657,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G452" s="4" t="n">
+      <c r="G452" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
@@ -36723,7 +36738,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G453" s="4" t="n">
+      <c r="G453" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
@@ -36804,7 +36819,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G454" s="4" t="n">
+      <c r="G454" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
@@ -36885,7 +36900,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G455" s="4" t="n">
+      <c r="G455" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
@@ -36966,7 +36981,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G456" s="4" t="n">
+      <c r="G456" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
@@ -37047,7 +37062,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G457" s="4" t="n">
+      <c r="G457" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
@@ -37128,7 +37143,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G458" s="4" t="n">
+      <c r="G458" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
@@ -37209,7 +37224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n">
+      <c r="G459" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
@@ -37290,7 +37305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n">
+      <c r="G460" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
@@ -37371,7 +37386,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n">
+      <c r="G461" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
@@ -37452,7 +37467,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G462" s="4" t="n">
+      <c r="G462" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
@@ -37533,7 +37548,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G463" s="4" t="n">
+      <c r="G463" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
@@ -37614,7 +37629,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G464" s="4" t="n">
+      <c r="G464" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
@@ -37695,7 +37710,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G465" s="4" t="n">
+      <c r="G465" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
@@ -37776,7 +37791,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G466" s="4" t="n">
+      <c r="G466" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
@@ -37857,7 +37872,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G467" s="4" t="n">
+      <c r="G467" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
@@ -37938,7 +37953,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G468" s="4" t="n">
+      <c r="G468" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
@@ -38019,7 +38034,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G469" s="4" t="n">
+      <c r="G469" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
@@ -38100,7 +38115,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G470" s="4" t="n">
+      <c r="G470" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H470" s="4" t="inlineStr">
@@ -38181,7 +38196,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G471" s="4" t="n">
+      <c r="G471" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H471" s="4" t="inlineStr">
@@ -38262,7 +38277,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G472" s="4" t="n">
+      <c r="G472" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H472" s="4" t="inlineStr">
@@ -38343,7 +38358,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G473" s="4" t="n">
+      <c r="G473" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H473" s="4" t="inlineStr">
@@ -38424,7 +38439,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G474" s="4" t="n">
+      <c r="G474" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H474" s="4" t="inlineStr">
@@ -38505,7 +38520,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G475" s="4" t="n">
+      <c r="G475" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H475" s="4" t="inlineStr">
@@ -38586,7 +38601,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G476" s="4" t="n">
+      <c r="G476" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H476" s="4" t="inlineStr">
@@ -38619,7 +38634,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N476" s="4" t="n">
+      <c r="N476" s="8" t="n">
         <v>1390889414.52148</v>
       </c>
       <c r="O476" s="4" t="inlineStr">
@@ -38665,7 +38680,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G477" s="4" t="n">
+      <c r="G477" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H477" s="4" t="inlineStr">
@@ -38698,7 +38713,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N477" s="4" t="n">
+      <c r="N477" s="8" t="n">
         <v>1366605304.15442</v>
       </c>
       <c r="O477" s="4" t="inlineStr">
@@ -38744,7 +38759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G478" s="4" t="n">
+      <c r="G478" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H478" s="4" t="inlineStr">
@@ -38777,7 +38792,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N478" s="4" t="n">
+      <c r="N478" s="8" t="n">
         <v>1489969151.60413</v>
       </c>
       <c r="O478" s="4" t="inlineStr">
@@ -38823,7 +38838,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G479" s="4" t="n">
+      <c r="G479" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H479" s="4" t="inlineStr">
@@ -38856,7 +38871,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N479" s="4" t="n">
+      <c r="N479" s="8" t="n">
         <v>1458861578.70202</v>
       </c>
       <c r="O479" s="4" t="inlineStr">
@@ -38902,7 +38917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G480" s="4" t="n">
+      <c r="G480" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H480" s="4" t="inlineStr">
@@ -38935,7 +38950,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N480" s="4" t="n">
+      <c r="N480" s="8" t="n">
         <v>1473655172.41379</v>
       </c>
       <c r="O480" s="4" t="inlineStr">
@@ -38981,7 +38996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G481" s="4" t="n">
+      <c r="G481" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H481" s="4" t="inlineStr">
@@ -39014,7 +39029,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N481" s="4" t="n">
+      <c r="N481" s="8" t="n">
         <v>1612822222.22222</v>
       </c>
       <c r="O481" s="4" t="inlineStr">
@@ -39060,7 +39075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G482" s="4" t="n">
+      <c r="G482" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H482" s="4" t="inlineStr">
@@ -39093,7 +39108,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N482" s="4" t="n">
+      <c r="N482" s="8" t="n">
         <v>1505288888.88889</v>
       </c>
       <c r="O482" s="4" t="inlineStr">
@@ -39139,7 +39154,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G483" s="4" t="n">
+      <c r="G483" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H483" s="4" t="inlineStr">
@@ -39172,7 +39187,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N483" s="4" t="n">
+      <c r="N483" s="8" t="n">
         <v>1612822222.22222</v>
       </c>
       <c r="O483" s="4" t="inlineStr">
@@ -39218,7 +39233,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G484" s="4" t="n">
+      <c r="G484" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H484" s="4" t="inlineStr">
@@ -39251,7 +39266,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N484" s="4" t="n">
+      <c r="N484" s="8" t="n">
         <v>1956888888.88889</v>
       </c>
       <c r="O484" s="4" t="inlineStr">
@@ -39297,7 +39312,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G485" s="4" t="n">
+      <c r="G485" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H485" s="4" t="inlineStr">
@@ -39330,7 +39345,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N485" s="4" t="n">
+      <c r="N485" s="8" t="n">
         <v>2042888888.88889</v>
       </c>
       <c r="O485" s="4" t="inlineStr">
@@ -39376,7 +39391,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G486" s="4" t="n">
+      <c r="G486" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H486" s="4" t="inlineStr">
@@ -39409,7 +39424,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N486" s="4" t="n">
+      <c r="N486" s="8" t="n">
         <v>2171911111.11111</v>
       </c>
       <c r="O486" s="4" t="inlineStr">
@@ -39455,7 +39470,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G487" s="4" t="n">
+      <c r="G487" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H487" s="4" t="inlineStr">
@@ -39488,7 +39503,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N487" s="4" t="n">
+      <c r="N487" s="8" t="n">
         <v>2463204545.45455</v>
       </c>
       <c r="O487" s="4" t="inlineStr">
@@ -39534,7 +39549,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G488" s="4" t="n">
+      <c r="G488" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H488" s="4" t="inlineStr">
@@ -39567,7 +39582,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N488" s="4" t="n">
+      <c r="N488" s="8" t="n">
         <v>2793090909.09091</v>
       </c>
       <c r="O488" s="4" t="inlineStr">
@@ -39613,7 +39628,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G489" s="4" t="n">
+      <c r="G489" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H489" s="4" t="inlineStr">
@@ -39646,7 +39661,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N489" s="4" t="n">
+      <c r="N489" s="8" t="n">
         <v>3263139534.88372</v>
       </c>
       <c r="O489" s="4" t="inlineStr">
@@ -39692,7 +39707,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G490" s="4" t="n">
+      <c r="G490" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H490" s="4" t="inlineStr">
@@ -39725,7 +39740,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N490" s="4" t="n">
+      <c r="N490" s="8" t="n">
         <v>4838441860.46512</v>
       </c>
       <c r="O490" s="4" t="inlineStr">
@@ -39771,7 +39786,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G491" s="4" t="n">
+      <c r="G491" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H491" s="4" t="inlineStr">
@@ -39804,7 +39819,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N491" s="4" t="n">
+      <c r="N491" s="8" t="n">
         <v>6863837209.30233</v>
       </c>
       <c r="O491" s="4" t="inlineStr">
@@ -39850,7 +39865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G492" s="4" t="n">
+      <c r="G492" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H492" s="4" t="inlineStr">
@@ -39883,7 +39898,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N492" s="4" t="n">
+      <c r="N492" s="8" t="n">
         <v>9069255813.953489</v>
       </c>
       <c r="O492" s="4" t="inlineStr">
@@ -39929,7 +39944,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G493" s="4" t="n">
+      <c r="G493" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H493" s="4" t="inlineStr">
@@ -39962,7 +39977,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N493" s="4" t="n">
+      <c r="N493" s="8" t="n">
         <v>12692465116.2791</v>
       </c>
       <c r="O493" s="4" t="inlineStr">
@@ -40008,7 +40023,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G494" s="4" t="n">
+      <c r="G494" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H494" s="4" t="inlineStr">
@@ -40041,7 +40056,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N494" s="4" t="n">
+      <c r="N494" s="8" t="n">
         <v>14650348837.2093</v>
       </c>
       <c r="O494" s="4" t="inlineStr">
@@ -40087,7 +40102,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G495" s="4" t="n">
+      <c r="G495" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H495" s="4" t="inlineStr">
@@ -40120,7 +40135,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N495" s="4" t="n">
+      <c r="N495" s="8" t="n">
         <v>13727674418.6047</v>
       </c>
       <c r="O495" s="4" t="inlineStr">
@@ -40166,7 +40181,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G496" s="4" t="n">
+      <c r="G496" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H496" s="4" t="inlineStr">
@@ -40199,7 +40214,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N496" s="4" t="n">
+      <c r="N496" s="8" t="n">
         <v>14627837209.3023</v>
       </c>
       <c r="O496" s="4" t="inlineStr">
@@ -40245,7 +40260,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G497" s="4" t="n">
+      <c r="G497" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H497" s="4" t="inlineStr">
@@ -40278,7 +40293,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N497" s="4" t="n">
+      <c r="N497" s="8" t="n">
         <v>16518209302.3256</v>
       </c>
       <c r="O497" s="4" t="inlineStr">
@@ -40324,7 +40339,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G498" s="4" t="n">
+      <c r="G498" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H498" s="4" t="inlineStr">
@@ -40357,7 +40372,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N498" s="4" t="n">
+      <c r="N498" s="8" t="n">
         <v>18971186046.5116</v>
       </c>
       <c r="O498" s="4" t="inlineStr">
@@ -40403,7 +40418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G499" s="4" t="n">
+      <c r="G499" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H499" s="4" t="inlineStr">
@@ -40436,7 +40451,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N499" s="4" t="n">
+      <c r="N499" s="8" t="n">
         <v>8799209302.325581</v>
       </c>
       <c r="O499" s="4" t="inlineStr">
@@ -40482,7 +40497,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G500" s="4" t="n">
+      <c r="G500" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H500" s="4" t="inlineStr">
@@ -40515,7 +40530,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N500" s="4" t="n">
+      <c r="N500" s="8" t="n">
         <v>10508123515.4394</v>
       </c>
       <c r="O500" s="4" t="inlineStr">
@@ -40561,7 +40576,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G501" s="4" t="n">
+      <c r="G501" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H501" s="4" t="inlineStr">
@@ -40594,7 +40609,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N501" s="4" t="n">
+      <c r="N501" s="7" t="n">
         <v>10466520000</v>
       </c>
       <c r="O501" s="4" t="inlineStr">
@@ -40640,7 +40655,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G502" s="4" t="n">
+      <c r="G502" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H502" s="4" t="inlineStr">
@@ -40673,7 +40688,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N502" s="4" t="n">
+      <c r="N502" s="8" t="n">
         <v>11927109278.3505</v>
       </c>
       <c r="O502" s="4" t="inlineStr">
@@ -40719,7 +40734,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G503" s="4" t="n">
+      <c r="G503" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H503" s="4" t="inlineStr">
@@ -40752,7 +40767,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N503" s="4" t="n">
+      <c r="N503" s="8" t="n">
         <v>10598117241.3793</v>
       </c>
       <c r="O503" s="4" t="inlineStr">
@@ -40798,7 +40813,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G504" s="4" t="n">
+      <c r="G504" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H504" s="4" t="inlineStr">
@@ -40831,7 +40846,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N504" s="4" t="n">
+      <c r="N504" s="8" t="n">
         <v>15910262068.9655</v>
       </c>
       <c r="O504" s="4" t="inlineStr">
@@ -40877,7 +40892,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G505" s="4" t="n">
+      <c r="G505" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H505" s="4" t="inlineStr">
@@ -40910,7 +40925,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N505" s="4" t="n">
+      <c r="N505" s="8" t="n">
         <v>8884312274.801821</v>
       </c>
       <c r="O505" s="4" t="inlineStr">
@@ -40956,7 +40971,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G506" s="4" t="n">
+      <c r="G506" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H506" s="4" t="inlineStr">
@@ -40989,7 +41004,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N506" s="4" t="n">
+      <c r="N506" s="8" t="n">
         <v>9493861738.048691</v>
       </c>
       <c r="O506" s="4" t="inlineStr">
@@ -41035,7 +41050,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G507" s="4" t="n">
+      <c r="G507" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H507" s="4" t="inlineStr">
@@ -41068,7 +41083,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N507" s="4" t="n">
+      <c r="N507" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O507" s="4" t="inlineStr">
@@ -41114,7 +41129,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G508" s="4" t="n">
+      <c r="G508" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H508" s="4" t="inlineStr">
@@ -41147,7 +41162,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N508" s="4" t="n">
+      <c r="N508" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O508" s="4" t="inlineStr">
@@ -41193,7 +41208,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G509" s="4" t="n">
+      <c r="G509" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H509" s="4" t="inlineStr">
@@ -41226,7 +41241,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N509" s="4" t="n">
+      <c r="N509" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O509" s="4" t="inlineStr">
@@ -41272,7 +41287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G510" s="4" t="n">
+      <c r="G510" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H510" s="4" t="inlineStr">
@@ -41305,7 +41320,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N510" s="4" t="n">
+      <c r="N510" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O510" s="4" t="inlineStr">
@@ -41351,7 +41366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G511" s="4" t="n">
+      <c r="G511" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H511" s="4" t="inlineStr">
@@ -41384,7 +41399,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N511" s="4" t="n">
+      <c r="N511" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O511" s="4" t="inlineStr">
@@ -41430,7 +41445,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G512" s="4" t="n">
+      <c r="G512" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H512" s="4" t="inlineStr">
@@ -41463,7 +41478,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N512" s="4" t="n">
+      <c r="N512" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O512" s="4" t="inlineStr">
@@ -41509,7 +41524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G513" s="4" t="n">
+      <c r="G513" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H513" s="4" t="inlineStr">
@@ -41542,7 +41557,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N513" s="4" t="n">
+      <c r="N513" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O513" s="4" t="inlineStr">
@@ -41588,7 +41603,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G514" s="4" t="n">
+      <c r="G514" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H514" s="4" t="inlineStr">
@@ -41621,7 +41636,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N514" s="4" t="n">
+      <c r="N514" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O514" s="4" t="inlineStr">
@@ -41667,7 +41682,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G515" s="4" t="n">
+      <c r="G515" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H515" s="4" t="inlineStr">
@@ -41700,7 +41715,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N515" s="4" t="n">
+      <c r="N515" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O515" s="4" t="inlineStr">
@@ -41746,7 +41761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G516" s="4" t="n">
+      <c r="G516" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H516" s="4" t="inlineStr">
@@ -41779,7 +41794,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N516" s="4" t="n">
+      <c r="N516" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O516" s="4" t="inlineStr">
@@ -41825,7 +41840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G517" s="4" t="n">
+      <c r="G517" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H517" s="4" t="inlineStr">
@@ -41858,7 +41873,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N517" s="4" t="n">
+      <c r="N517" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O517" s="4" t="inlineStr">
@@ -41904,7 +41919,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G518" s="4" t="n">
+      <c r="G518" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H518" s="4" t="inlineStr">
@@ -41937,7 +41952,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N518" s="4" t="n">
+      <c r="N518" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O518" s="4" t="inlineStr">
@@ -41983,7 +41998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G519" s="4" t="n">
+      <c r="G519" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H519" s="4" t="inlineStr">
@@ -42016,7 +42031,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N519" s="4" t="n">
+      <c r="N519" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O519" s="4" t="inlineStr">
@@ -42062,7 +42077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G520" s="4" t="n">
+      <c r="G520" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H520" s="4" t="inlineStr">
@@ -42095,7 +42110,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N520" s="4" t="n">
+      <c r="N520" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O520" s="4" t="inlineStr">
@@ -42141,7 +42156,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G521" s="4" t="n">
+      <c r="G521" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H521" s="4" t="inlineStr">
@@ -42174,7 +42189,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N521" s="4" t="n">
+      <c r="N521" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O521" s="4" t="inlineStr">
@@ -42220,7 +42235,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G522" s="4" t="n">
+      <c r="G522" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H522" s="4" t="inlineStr">
@@ -42253,7 +42268,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N522" s="4" t="n">
+      <c r="N522" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O522" s="4" t="inlineStr">
@@ -42299,7 +42314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G523" s="4" t="n">
+      <c r="G523" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H523" s="4" t="inlineStr">
@@ -42332,7 +42347,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N523" s="4" t="n">
+      <c r="N523" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O523" s="4" t="inlineStr">
@@ -42378,7 +42393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G524" s="4" t="n">
+      <c r="G524" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H524" s="4" t="inlineStr">
@@ -42411,7 +42426,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N524" s="4" t="n">
+      <c r="N524" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O524" s="4" t="inlineStr">
@@ -42457,7 +42472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G525" s="4" t="n">
+      <c r="G525" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H525" s="4" t="inlineStr">
@@ -42490,7 +42505,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N525" s="4" t="n">
+      <c r="N525" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O525" s="4" t="inlineStr">
@@ -42536,7 +42551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G526" s="4" t="n">
+      <c r="G526" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H526" s="4" t="inlineStr">
@@ -42569,7 +42584,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N526" s="4" t="n">
+      <c r="N526" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O526" s="4" t="inlineStr">
@@ -42615,7 +42630,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G527" s="4" t="n">
+      <c r="G527" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H527" s="4" t="inlineStr">
@@ -42648,7 +42663,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N527" s="4" t="n">
+      <c r="N527" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O527" s="4" t="inlineStr">
@@ -42694,7 +42709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G528" s="4" t="n">
+      <c r="G528" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H528" s="4" t="inlineStr">
@@ -42727,7 +42742,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N528" s="4" t="n">
+      <c r="N528" s="8" t="n">
         <v>78668126778.4577</v>
       </c>
       <c r="O528" s="4" t="inlineStr">
@@ -42773,7 +42788,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G529" s="4" t="n">
+      <c r="G529" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H529" s="4" t="inlineStr">
@@ -42806,7 +42821,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N529" s="4" t="n">
+      <c r="N529" s="8" t="n">
         <v>83592737983.1543</v>
       </c>
       <c r="O529" s="4" t="inlineStr">
@@ -42852,7 +42867,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G530" s="4" t="n">
+      <c r="G530" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H530" s="4" t="inlineStr">
@@ -42885,7 +42900,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N530" s="4" t="n">
+      <c r="N530" s="8" t="n">
         <v>44352366681.2494</v>
       </c>
       <c r="O530" s="4" t="inlineStr">
@@ -42931,7 +42946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G531" s="4" t="n">
+      <c r="G531" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H531" s="4" t="inlineStr">
@@ -42964,7 +42979,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N531" s="4" t="n">
+      <c r="N531" s="8" t="n">
         <v>24577347080.6935</v>
       </c>
       <c r="O531" s="4" t="inlineStr">
@@ -43010,7 +43025,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G532" s="4" t="n">
+      <c r="G532" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H532" s="4" t="inlineStr">
@@ -43043,7 +43058,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N532" s="4" t="n">
+      <c r="N532" s="8" t="n">
         <v>11515036487.7869</v>
       </c>
       <c r="O532" s="4" t="inlineStr">
@@ -43089,7 +43104,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G533" s="4" t="n">
+      <c r="G533" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H533" s="4" t="inlineStr">
@@ -43122,7 +43137,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N533" s="4" t="n">
+      <c r="N533" s="8" t="n">
         <v>10756686685.3221</v>
       </c>
       <c r="O533" s="4" t="inlineStr">
@@ -43168,7 +43183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G534" s="4" t="n">
+      <c r="G534" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H534" s="4" t="inlineStr">
@@ -43201,7 +43216,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N534" s="4" t="n">
+      <c r="N534" s="8" t="n">
         <v>12326332794.8304</v>
       </c>
       <c r="O534" s="4" t="inlineStr">
@@ -43247,7 +43262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G535" s="4" t="n">
+      <c r="G535" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H535" s="4" t="inlineStr">
@@ -43280,7 +43295,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N535" s="4" t="n">
+      <c r="N535" s="8" t="n">
         <v>7982721068.68012</v>
       </c>
       <c r="O535" s="4" t="inlineStr">
@@ -43326,7 +43341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G536" s="4" t="n">
+      <c r="G536" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H536" s="4" t="inlineStr">
@@ -43359,7 +43374,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N536" s="4" t="n">
+      <c r="N536" s="8" t="n">
         <v>5605400728.82019</v>
       </c>
       <c r="O536" s="4" t="inlineStr">
@@ -43405,7 +43420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G537" s="4" t="n">
+      <c r="G537" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H537" s="4" t="inlineStr">
@@ -43438,7 +43453,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N537" s="4" t="n">
+      <c r="N537" s="8" t="n">
         <v>7856090323.7093</v>
       </c>
       <c r="O537" s="4" t="inlineStr">
@@ -43484,7 +43499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G538" s="4" t="n">
+      <c r="G538" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H538" s="4" t="inlineStr">
@@ -43517,7 +43532,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N538" s="4" t="n">
+      <c r="N538" s="8" t="n">
         <v>10280104686.5588</v>
       </c>
       <c r="O538" s="4" t="inlineStr">
@@ -43563,7 +43578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G539" s="4" t="n">
+      <c r="G539" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H539" s="4" t="inlineStr">
@@ -43596,7 +43611,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N539" s="4" t="n">
+      <c r="N539" s="8" t="n">
         <v>10266483008.9548</v>
       </c>
       <c r="O539" s="4" t="inlineStr">
@@ -43642,7 +43657,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G540" s="4" t="n">
+      <c r="G540" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H540" s="4" t="inlineStr">
@@ -43675,7 +43690,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N540" s="4" t="n">
+      <c r="N540" s="8" t="n">
         <v>11456619838.8081</v>
       </c>
       <c r="O540" s="4" t="inlineStr">
@@ -43721,7 +43736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G541" s="4" t="n">
+      <c r="G541" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H541" s="4" t="inlineStr">
@@ -43754,7 +43769,7 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N541" s="4" t="n">
+      <c r="N541" s="8" t="n">
         <v>10074121350.14</v>
       </c>
       <c r="O541" s="4" t="inlineStr">
@@ -43800,7 +43815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G542" s="4" t="n">
+      <c r="G542" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H542" s="4" t="inlineStr">
@@ -43881,7 +43896,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G543" s="4" t="n">
+      <c r="G543" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H543" s="4" t="inlineStr">
@@ -43962,7 +43977,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G544" s="4" t="n">
+      <c r="G544" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H544" s="4" t="inlineStr">
@@ -44043,7 +44058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G545" s="4" t="n">
+      <c r="G545" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H545" s="4" t="inlineStr">
@@ -44124,7 +44139,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G546" s="4" t="n">
+      <c r="G546" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H546" s="4" t="inlineStr">
@@ -44205,7 +44220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G547" s="4" t="n">
+      <c r="G547" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H547" s="4" t="inlineStr">
@@ -44286,7 +44301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G548" s="4" t="n">
+      <c r="G548" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H548" s="4" t="inlineStr">
@@ -44367,7 +44382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G549" s="4" t="n">
+      <c r="G549" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H549" s="4" t="inlineStr">
@@ -44448,7 +44463,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G550" s="4" t="n">
+      <c r="G550" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H550" s="4" t="inlineStr">
@@ -44529,7 +44544,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G551" s="4" t="n">
+      <c r="G551" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H551" s="4" t="inlineStr">
@@ -44610,7 +44625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G552" s="4" t="n">
+      <c r="G552" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H552" s="4" t="inlineStr">
@@ -44691,7 +44706,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G553" s="4" t="n">
+      <c r="G553" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H553" s="4" t="inlineStr">
@@ -44772,7 +44787,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G554" s="4" t="n">
+      <c r="G554" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H554" s="4" t="inlineStr">
@@ -44853,7 +44868,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G555" s="4" t="n">
+      <c r="G555" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H555" s="4" t="inlineStr">
@@ -44934,7 +44949,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G556" s="4" t="n">
+      <c r="G556" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H556" s="4" t="inlineStr">
@@ -45015,7 +45030,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G557" s="4" t="n">
+      <c r="G557" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H557" s="4" t="inlineStr">
@@ -45096,7 +45111,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G558" s="4" t="n">
+      <c r="G558" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H558" s="4" t="inlineStr">
@@ -45177,7 +45192,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G559" s="4" t="n">
+      <c r="G559" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H559" s="4" t="inlineStr">
@@ -45258,7 +45273,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G560" s="4" t="n">
+      <c r="G560" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H560" s="4" t="inlineStr">
@@ -45339,7 +45354,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G561" s="4" t="n">
+      <c r="G561" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H561" s="4" t="inlineStr">
@@ -45420,7 +45435,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G562" s="4" t="n">
+      <c r="G562" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H562" s="4" t="inlineStr">
@@ -45501,7 +45516,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G563" s="4" t="n">
+      <c r="G563" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H563" s="4" t="inlineStr">
@@ -45582,7 +45597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G564" s="4" t="n">
+      <c r="G564" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H564" s="4" t="inlineStr">
@@ -45663,7 +45678,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G565" s="4" t="n">
+      <c r="G565" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H565" s="4" t="inlineStr">
@@ -45744,7 +45759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G566" s="4" t="n">
+      <c r="G566" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H566" s="4" t="inlineStr">
@@ -45825,7 +45840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G567" s="4" t="n">
+      <c r="G567" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H567" s="4" t="inlineStr">
@@ -45906,7 +45921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G568" s="4" t="n">
+      <c r="G568" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H568" s="4" t="inlineStr">
@@ -45987,7 +46002,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G569" s="4" t="n">
+      <c r="G569" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H569" s="4" t="inlineStr">
@@ -46068,7 +46083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G570" s="4" t="n">
+      <c r="G570" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H570" s="4" t="inlineStr">
@@ -46149,7 +46164,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G571" s="4" t="n">
+      <c r="G571" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H571" s="4" t="inlineStr">
@@ -46230,7 +46245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G572" s="4" t="n">
+      <c r="G572" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H572" s="4" t="inlineStr">
@@ -46311,7 +46326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G573" s="4" t="n">
+      <c r="G573" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H573" s="4" t="inlineStr">
@@ -46392,7 +46407,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G574" s="4" t="n">
+      <c r="G574" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H574" s="4" t="inlineStr">
@@ -46473,7 +46488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G575" s="4" t="n">
+      <c r="G575" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H575" s="4" t="inlineStr">
@@ -46554,7 +46569,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G576" s="4" t="n">
+      <c r="G576" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H576" s="4" t="inlineStr">
@@ -46635,7 +46650,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G577" s="4" t="n">
+      <c r="G577" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H577" s="4" t="inlineStr">
@@ -46716,7 +46731,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G578" s="4" t="n">
+      <c r="G578" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H578" s="4" t="inlineStr">
@@ -46797,7 +46812,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G579" s="4" t="n">
+      <c r="G579" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H579" s="4" t="inlineStr">
@@ -46878,7 +46893,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G580" s="4" t="n">
+      <c r="G580" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H580" s="4" t="inlineStr">
@@ -46959,7 +46974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G581" s="4" t="n">
+      <c r="G581" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H581" s="4" t="inlineStr">
@@ -47040,7 +47055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G582" s="4" t="n">
+      <c r="G582" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H582" s="4" t="inlineStr">
@@ -47121,7 +47136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G583" s="4" t="n">
+      <c r="G583" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H583" s="4" t="inlineStr">
@@ -47202,7 +47217,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G584" s="4" t="n">
+      <c r="G584" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H584" s="4" t="inlineStr">
@@ -47283,7 +47298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G585" s="4" t="n">
+      <c r="G585" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H585" s="4" t="inlineStr">
@@ -47364,7 +47379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G586" s="4" t="n">
+      <c r="G586" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H586" s="4" t="inlineStr">
@@ -47445,7 +47460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G587" s="4" t="n">
+      <c r="G587" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H587" s="4" t="inlineStr">
@@ -47526,7 +47541,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G588" s="4" t="n">
+      <c r="G588" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H588" s="4" t="inlineStr">
@@ -47607,7 +47622,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G589" s="4" t="n">
+      <c r="G589" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H589" s="4" t="inlineStr">
@@ -47688,7 +47703,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G590" s="4" t="n">
+      <c r="G590" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H590" s="4" t="inlineStr">
@@ -47769,7 +47784,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G591" s="4" t="n">
+      <c r="G591" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H591" s="4" t="inlineStr">
@@ -47850,7 +47865,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G592" s="4" t="n">
+      <c r="G592" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H592" s="4" t="inlineStr">
@@ -47931,7 +47946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G593" s="4" t="n">
+      <c r="G593" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H593" s="4" t="inlineStr">
@@ -48012,7 +48027,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G594" s="4" t="n">
+      <c r="G594" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H594" s="4" t="inlineStr">
@@ -48093,7 +48108,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G595" s="4" t="n">
+      <c r="G595" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H595" s="4" t="inlineStr">
@@ -48174,7 +48189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G596" s="4" t="n">
+      <c r="G596" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H596" s="4" t="inlineStr">
@@ -48255,7 +48270,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G597" s="4" t="n">
+      <c r="G597" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H597" s="4" t="inlineStr">
@@ -48336,7 +48351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G598" s="4" t="n">
+      <c r="G598" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H598" s="4" t="inlineStr">
@@ -48417,7 +48432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G599" s="4" t="n">
+      <c r="G599" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H599" s="4" t="inlineStr">
@@ -48498,7 +48513,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G600" s="4" t="n">
+      <c r="G600" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H600" s="4" t="inlineStr">
@@ -48579,7 +48594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G601" s="4" t="n">
+      <c r="G601" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H601" s="4" t="inlineStr">
@@ -48660,7 +48675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G602" s="4" t="n">
+      <c r="G602" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H602" s="4" t="inlineStr">
@@ -48741,7 +48756,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G603" s="4" t="n">
+      <c r="G603" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H603" s="4" t="inlineStr">
@@ -48822,7 +48837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G604" s="4" t="n">
+      <c r="G604" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H604" s="4" t="inlineStr">
@@ -48903,7 +48918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G605" s="4" t="n">
+      <c r="G605" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H605" s="4" t="inlineStr">
@@ -48984,7 +48999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G606" s="4" t="n">
+      <c r="G606" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H606" s="4" t="inlineStr">
@@ -49065,7 +49080,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G607" s="4" t="n">
+      <c r="G607" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H607" s="4" t="inlineStr">
@@ -49146,7 +49161,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G608" s="4" t="n">
+      <c r="G608" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H608" s="4" t="inlineStr">
@@ -49286,7 +49301,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>9</v>
       </c>
     </row>
@@ -49296,7 +49311,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>602</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23821,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36474,7 +36474,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36553,7 +36553,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36790,7 +36790,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37659,7 +37659,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38054,7 +38054,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38133,7 +38133,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38370,7 +38370,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38449,7 +38449,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38607,7 +38607,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38923,7 +38923,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39002,7 +39002,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39239,7 +39239,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39476,7 +39476,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39871,7 +39871,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39950,7 +39950,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40108,7 +40108,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40187,7 +40187,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40266,7 +40266,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40424,7 +40424,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40661,7 +40661,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40819,7 +40819,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40977,7 +40977,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41451,7 +41451,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41688,7 +41688,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41925,7 +41925,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42162,7 +42162,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42478,7 +42478,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42557,7 +42557,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42952,7 +42952,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43426,7 +43426,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43584,7 +43584,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43663,7 +43663,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43900,7 +43900,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44216,7 +44216,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44532,7 +44532,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44611,7 +44611,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44690,7 +44690,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44769,7 +44769,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44848,7 +44848,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44927,7 +44927,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45085,7 +45085,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45164,7 +45164,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45243,7 +45243,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45796,7 +45796,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45954,7 +45954,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46033,7 +46033,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46191,7 +46191,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46270,7 +46270,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46744,7 +46744,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46902,7 +46902,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47218,7 +47218,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47303,7 +47303,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23821,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36474,7 +36474,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36553,7 +36553,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36790,7 +36790,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37659,7 +37659,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38054,7 +38054,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38133,7 +38133,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38370,7 +38370,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38449,7 +38449,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38607,7 +38607,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38923,7 +38923,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39002,7 +39002,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39239,7 +39239,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39476,7 +39476,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39871,7 +39871,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39950,7 +39950,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40108,7 +40108,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40187,7 +40187,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40266,7 +40266,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40424,7 +40424,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40661,7 +40661,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40819,7 +40819,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40977,7 +40977,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41451,7 +41451,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41688,7 +41688,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41925,7 +41925,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42162,7 +42162,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42478,7 +42478,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42557,7 +42557,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42952,7 +42952,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43426,7 +43426,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43584,7 +43584,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43663,7 +43663,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43900,7 +43900,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44216,7 +44216,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44532,7 +44532,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44611,7 +44611,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44690,7 +44690,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44769,7 +44769,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44848,7 +44848,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44927,7 +44927,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45085,7 +45085,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45164,7 +45164,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45243,7 +45243,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45796,7 +45796,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45954,7 +45954,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46033,7 +46033,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46191,7 +46191,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46270,7 +46270,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46744,7 +46744,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46902,7 +46902,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47218,7 +47218,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47303,7 +47303,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23821,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36474,7 +36474,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36553,7 +36553,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36790,7 +36790,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37659,7 +37659,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38054,7 +38054,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38133,7 +38133,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38370,7 +38370,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38449,7 +38449,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38607,7 +38607,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38923,7 +38923,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39002,7 +39002,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39239,7 +39239,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39476,7 +39476,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39871,7 +39871,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39950,7 +39950,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40108,7 +40108,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40187,7 +40187,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40266,7 +40266,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40424,7 +40424,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40661,7 +40661,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40819,7 +40819,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40977,7 +40977,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41451,7 +41451,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41688,7 +41688,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41925,7 +41925,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42162,7 +42162,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42478,7 +42478,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42557,7 +42557,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42952,7 +42952,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43426,7 +43426,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43584,7 +43584,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43663,7 +43663,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43900,7 +43900,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44216,7 +44216,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44532,7 +44532,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44611,7 +44611,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44690,7 +44690,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44769,7 +44769,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44848,7 +44848,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44927,7 +44927,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45085,7 +45085,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45164,7 +45164,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45243,7 +45243,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45796,7 +45796,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45954,7 +45954,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46033,7 +46033,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46191,7 +46191,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46270,7 +46270,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46744,7 +46744,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46902,7 +46902,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47218,7 +47218,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47303,7 +47303,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
